--- a/stories/arbres/ATOM-EMO.LEX.007-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nino est dans le salon. Papa lit. Nino veut un jeu. Ses jambes bougent. Son corps ne tient pas. Nino dit : je suis nerveux. Être nerveux, ce n'est pas honteux. Nino dit : je demande une pause. Papa dit : oui. Nino s'assoit. Il pose les pieds. Il souffle. Ses jambes se calment. Papa sourit. Papa dit : une pause, c'est bien.</t>
+          <t>Nino est dans le salon. Papa lit. Nino veut un jeu. Ses jambes bougent. Son corps ne tient pas. Je suis nerveux. Être nerveux, ce n'est pas honteux. Je demande une pause. Oui. Nino s'assoit. Il pose les pieds. Il souffle. Ses jambes se calment. Papa sourit. Une pause, c'est bien.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nino est dans le salon. Papa lit. Nino veut un jeu. Ses jambes bougent. Son corps ne tient pas.
+enfant-m|Je suis nerveux. Être nerveux, ce n'est pas honteux.
+enfant-m|Je demande une pause.
+papa|Oui.
+narrateur|Nino s'assoit. Il pose les pieds. Il souffle. Ses jambes se calment. Papa sourit.
+papa|Une pause, c'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Nino ne tient plus. Que demande-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a nommé : nerveux. Il a demandé une pause. Il s'est assis. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Nino boit un peu d'eau. Papa lui tend un livre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 papa|Une pause, c'est bien.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Nino ne tient plus. Que demande-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Nino a nommé : nerveux. Il a demandé une pause. Il s'est assis. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Nino boit un peu d'eau. Papa lui tend un livre.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.007-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nino est nerveux</t>
+          <t>Nino demande une pause</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Papa lit. Nino veut un jeu. Ses jambes bougent. Il nomme nerveux, demande une pause, s'assoit.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nino est dans le salon. Papa lit. Nino veut un jeu. Ses jambes bougent. Son corps ne tient pas. Je suis nerveux. Être nerveux, ce n'est pas honteux. Je demande une pause. Oui. Nino s'assoit. Il pose les pieds. Il souffle. Ses jambes se calment. Papa sourit. Une pause, c'est bien.</t>
+          <t>Les pages du livre font un bruit doux. Chut, chut, une page, puis une autre. La lampe dessine un rond jaune. Le rond tombe sur le canapé. Les chaussettes de papa sont rouges. Elles dépassent un peu du fauteuil. J'aime ce petit bruit, Nino. Les pages parlent tout bas. Oui. Le livre est calme. Un coussin rayé attend au milieu. Il est mou, comme un nuage. Tu veux le coussin, Nino ? Oui, papa. En ce moment, Nino est au salon. Il veut un jeu, tout de suite. Ses jambes bougent. Ses pieds tapent le tapis. Son corps ne tient pas. Je suis nerveux. Mes jambes bougent. Être nerveux, ce n'est pas honteux. On peut demander une pause. Je demande une pause. Oui, Nino. On s'assoit. Nino s'assoit. Il pose les pieds au tapis. Les pieds sont posés. Tu souffles avec moi ? Oui. Nino souffle. Ses jambes se calment. Une pause, c'est bien. Bravo, Nino. C'est du bon travail. Tu as demandé la pause ? Oui, papa. Je suis nerveux. Tu as nommé. Tu t'es assis. Le rond jaune de la lampe est calme. Les pages ne bougent plus. Tu veux un peu d'eau ? Oui. Nino boit un peu d'eau. Les jambes sont plus douces ? Oui. Elles bougent moins. On peut regarder le livre, après. Les pages parlent tout bas. Oui. Tout bas. Les chaussettes rouges bougent un peu. Papa rapproche le livre. Tu restes assis ? Oui, papa. Le coussin rayé est chaud sous Nino. Le tapis est doux sous les pieds. On reste dans le rond jaune. C'est doux. Oui. C'est doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,76 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Nino est dans le salon. Papa lit. Nino veut un jeu. Ses jambes bougent. Son corps ne tient pas.
-enfant-m|Je suis nerveux. Être nerveux, ce n'est pas honteux.
+          <t>narrateur|Les pages du livre font un bruit doux.
+narrateur|Chut, chut, une page, puis une autre.
+narrateur|La lampe dessine un rond jaune.
+narrateur|Le rond tombe sur le canapé.
+narrateur|Les chaussettes de papa sont rouges.
+narrateur|Elles dépassent un peu du fauteuil.
+papa|J'aime ce petit bruit, Nino.
+enfant-m|Les pages parlent tout bas.
+papa|Oui.
+papa|Le livre est calme.
+narrateur|Un coussin rayé attend au milieu.
+narrateur|Il est mou, comme un nuage.
+papa|Tu veux le coussin, Nino ?
+enfant-m|Oui, papa.
+narrateur|En ce moment, Nino est au salon.
+narrateur|Il veut un jeu, tout de suite.
+narrateur|Ses jambes bougent.
+narrateur|Ses pieds tapent le tapis.
+narrateur|Son corps ne tient pas.
+enfant-m|Je suis nerveux.
+enfant-m|Mes jambes bougent.
+papa|Être nerveux, ce n'est pas honteux.
+papa|On peut demander une pause.
 enfant-m|Je demande une pause.
+papa|Oui, Nino.
+papa|On s'assoit.
+narrateur|Nino s'assoit.
+narrateur|Il pose les pieds au tapis.
+papa|Les pieds sont posés.
+papa|Tu souffles avec moi ?
+enfant-m|Oui.
+narrateur|Nino souffle.
+narrateur|Ses jambes se calment.
+papa|Une pause, c'est bien.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+papa|Tu as demandé la pause ?
+enfant-m|Oui, papa.
+enfant-m|Je suis nerveux.
+papa|Tu as nommé.
+papa|Tu t'es assis.
+narrateur|Le rond jaune de la lampe est calme.
+narrateur|Les pages ne bougent plus.
+papa|Tu veux un peu d'eau ?
+enfant-m|Oui.
+narrateur|Nino boit un peu d'eau.
+papa|Les jambes sont plus douces ?
+enfant-m|Oui.
+enfant-m|Elles bougent moins.
+papa|On peut regarder le livre, après.
+enfant-m|Les pages parlent tout bas.
 papa|Oui.
-narrateur|Nino s'assoit. Il pose les pieds. Il souffle. Ses jambes se calment. Papa sourit.
-papa|Une pause, c'est bien.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Tout bas.
+narrateur|Les chaussettes rouges bougent un peu.
+narrateur|Papa rapproche le livre.
+papa|Tu restes assis ?
+enfant-m|Oui, papa.
+narrateur|Le coussin rayé est chaud sous Nino.
+narrateur|Le tapis est doux sous les pieds.
+papa|On reste dans le rond jaune.
+enfant-m|C'est doux.
+papa|Oui.
+papa|C'est doux.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pages_livre</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,7 +1574,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Nino ne tient plus. Que demande-t-il ?</t>
+          <t>narrateur|Nino ne tient plus.
+narrateur|Que demande-t-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1529,7 +1603,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a nommé : nerveux. Il a demandé une pause. Il s'est assis. Papa était là.</t>
+          <t>Nino a nommé : nerveux. Il a demandé une pause. Il s'est assis. Bravo, Nino. Tu as demandé une pause. C'est du bon travail. Je suis nerveux. J'ai demandé une pause. Oui. Tu t'es assis. Les pieds sont posés ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,7 +1747,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nino a nommé : nerveux. Il a demandé une pause. Il s'est assis. Papa était là.</t>
+          <t>narrateur|Nino a nommé : nerveux.
+narrateur|Il a demandé une pause.
+narrateur|Il s'est assis.
+papa|Bravo, Nino.
+papa|Tu as demandé une pause.
+papa|C'est du bon travail.
+enfant-m|Je suis nerveux.
+enfant-m|J'ai demandé une pause.
+papa|Oui.
+papa|Tu t'es assis.
+papa|Les pieds sont posés ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1786,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino boit un peu d'eau. Papa lui tend un livre.</t>
+          <t>Nino boit encore un peu d'eau. Papa lui tend le livre. On tourne une page ? Oui. Tout bas. Une page fait chut. Le rond jaune tremble un peu. Tu restes assis près de moi ? Oui, papa. Les chaussettes rouges sont immobiles. Le coussin rayé est encore chaud. La pause a aidé.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1837,7 +1922,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nino boit un peu d'eau. Papa lui tend un livre.</t>
+          <t>narrateur|Nino boit encore un peu d'eau.
+narrateur|Papa lui tend le livre.
+papa|On tourne une page ?
+enfant-m|Oui.
+enfant-m|Tout bas.
+narrateur|Une page fait chut.
+narrateur|Le rond jaune tremble un peu.
+papa|Tu restes assis près de moi ?
+enfant-m|Oui, papa.
+narrateur|Les chaussettes rouges sont immobiles.
+narrateur|Le coussin rayé est encore chaud.
+papa|La pause a aidé.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1865,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai demandé une pause. J'étais nerveux. Bravo. Tu as fait du bon travail. Le rond jaune de la lampe reste là. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2005,7 +2101,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai demandé une pause.
+enfant-m|J'étais nerveux.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le rond jaune de la lampe reste là.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2027,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2166,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les pages du livre font un bruit doux. Chut, chut, une page, puis une autre. La lampe dessine un rond jaune. Le rond tombe sur le canapé. Les chaussettes de papa sont rouges. Elles dépassent un peu du fauteuil. J'aime ce petit bruit, Nino. Les pages parlent tout bas. Oui. Le livre est calme. Un coussin rayé attend au milieu. Il est mou, comme un nuage. Tu veux le coussin, Nino ? Oui, papa. En ce moment, Nino est au salon. Il veut un jeu, tout de suite. Ses jambes bougent. Ses pieds tapent le tapis. Son corps ne tient pas. Je suis nerveux. Mes jambes bougent. Être nerveux, ce n'est pas honteux. On peut demander une pause. Je demande une pause. Oui, Nino. On s'assoit. Nino s'assoit. Il pose les pieds au tapis. Les pieds sont posés. Tu souffles avec moi ? Oui. Nino souffle. Ses jambes se calment. Une pause, c'est bien. Bravo, Nino. C'est du bon travail. Tu as demandé la pause ? Oui, papa. Je suis nerveux. Tu as nommé. Tu t'es assis. Le rond jaune de la lampe est calme. Les pages ne bougent plus. Tu veux un peu d'eau ? Oui. Nino boit un peu d'eau. Les jambes sont plus douces ? Oui. Elles bougent moins. On peut regarder le livre, après. Les pages parlent tout bas. Oui. Tout bas. Les chaussettes rouges bougent un peu. Papa rapproche le livre. Tu restes assis ? Oui, papa. Le coussin rayé est chaud sous Nino. Le tapis est doux sous les pieds. On reste dans le rond jaune. C'est doux. Oui. C'est doux.</t>
+          <t>Les pages du livre font un bruit doux. Chut, chut, une page, puis une autre. La lampe dessine un rond jaune. Le rond tombe sur le canapé. Les chaussettes de papa sont rouges. Elles dépassent un peu du fauteuil. J'aime ce petit bruit, Nino. Les pages parlent tout bas. Oui. Le livre est calme. Un coussin rayé attend au milieu. Il est mou, comme un nuage. Tu veux le coussin, Nino ? Oui, papa. En ce moment, Nino est au salon. Il veut un jeu, tout de suite. Ses jambes bougent. Ses pieds tapent le tapis. Son corps ne tient pas. Je suis nerveux. Mes jambes bougent. Être nerveux, ce n'est pas honteux. On peut demander une pause. Je demande une pause. Oui, Nino. On s'assoit. Nino s'assoit. Il pose les pieds au tapis. Les pieds sont posés. Tu souffles avec moi ? Oui. Nino souffle. Ses jambes se calment. Une pause, c'est bien. Bravo, Nino. Tu as demandé la pause ? Oui, papa. Je suis nerveux. Tu as nommé. Tu t'es assis. Le rond jaune de la lampe est calme. Les pages ne bougent plus. Tu veux un peu d'eau ? Oui. Nino boit un peu d'eau. Les jambes sont plus douces ? Oui. Elles bougent moins. On peut regarder le livre, après. Les pages parlent tout bas. Oui. Tout bas. Les chaussettes rouges bougent un peu. Papa rapproche le livre. Tu restes assis ? Oui, papa. Le coussin rayé est chaud sous Nino. Le tapis est doux sous les pieds. On reste dans le rond jaune. C'est doux. Oui. C'est doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nino est dans le salon. Papa lit. Nino veut un jeu. Ses jambes bougent. Son corps ne tient pas. Nino dit : je suis &lt;emphasis level="moderate"&gt;nerveux&lt;/emphasis&gt;. Être nerveux, ce n'est pas honteux. Nino dit : je demande une pause. Papa dit : oui. Nino s'assoit. Il pose les pieds. Il souffle. Ses jambes se calment. Papa sourit. Papa dit : une pause, c'est bien.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les pages du livre font un bruit doux. Chut, chut, une page, puis une autre. La lampe dessine un rond jaune. Le rond tombe sur le canapé. Les chaussettes de papa sont rouges. Elles dépassent un peu du fauteuil. J'aime ce petit bruit, Nino. Les pages parlent tout bas. Oui. Le livre est calme. Un coussin rayé attend au milieu. Il est mou, comme un nuage. Tu veux le coussin, Nino ? Oui, papa. En ce moment, Nino est au salon. Il veut un jeu, tout de suite. Ses jambes bougent. Ses pieds tapent le tapis. Son corps ne tient pas. Je suis nerveux. Mes jambes bougent. Être nerveux, ce n'est pas honteux. On peut demander une pause. Je demande une pause. Oui, Nino. On s'assoit. Nino s'assoit. Il pose les pieds au tapis. Les pieds sont posés. Tu souffles avec moi ? Oui. Nino souffle. Ses jambes se calment. Une pause, c'est bien. Bravo, Nino. Tu as demandé la pause ? Oui, papa. Je suis nerveux. Tu as nommé. Tu t'es assis. Le rond jaune de la lampe est calme. Les pages ne bougent plus. Tu veux un peu d'eau ? Oui. Nino boit un peu d'eau. Les jambes sont plus douces ? Oui. Elles bougent moins. On peut regarder le livre, après. Les pages parlent tout bas. Oui. Tout bas. Les chaussettes rouges bougent un peu. Papa rapproche le livre. Tu restes assis ? Oui, papa. Le coussin rayé est chaud sous Nino. Le tapis est doux sous les pieds. On reste dans le rond jaune. C'est doux. Oui. C'est doux.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1359,7 +1359,6 @@
 narrateur|Ses jambes se calment.
 papa|Une pause, c'est bien.
 papa|Bravo, Nino.
-papa|C'est du bon travail.
 papa|Tu as demandé la pause ?
 enfant-m|Oui, papa.
 enfant-m|Je suis nerveux.
@@ -1423,7 +1422,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nino ne tient plus. Que demande-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino ne tient plus. Que demande-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1578,7 +1577,6 @@
 narrateur|Que demande-t-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1603,12 +1601,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a nommé : nerveux. Il a demandé une pause. Il s'est assis. Bravo, Nino. Tu as demandé une pause. C'est du bon travail. Je suis nerveux. J'ai demandé une pause. Oui. Tu t'es assis. Les pieds sont posés ? Oui, papa.</t>
+          <t>Nino a nommé : nerveux. Il a demandé une pause. Il s'est assis. Bravo, Nino. Tu as demandé une pause. Je suis nerveux. J'ai demandé une pause. Oui. Tu t'es assis. Les pieds sont posés ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nino a nommé : &lt;emphasis level="moderate"&gt;nerveux&lt;/emphasis&gt;. Il a demandé une pause. Il s'est assis. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a nommé : nerveux. Il a demandé une pause. Il s'est assis. Bravo, Nino. Tu as demandé une pause. Je suis nerveux. J'ai demandé une pause. Oui. Tu t'es assis. Les pieds sont posés ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1752,7 +1750,6 @@
 narrateur|Il s'est assis.
 papa|Bravo, Nino.
 papa|Tu as demandé une pause.
-papa|C'est du bon travail.
 enfant-m|Je suis nerveux.
 enfant-m|J'ai demandé une pause.
 papa|Oui.
@@ -1761,7 +1758,6 @@
 enfant-m|Oui, papa.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,7 +1787,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nino boit un peu d'eau. Papa lui tend un livre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino boit encore un peu d'eau. Papa lui tend le livre. On tourne une page ? Oui. Tout bas. Une page fait chut. Le rond jaune tremble un peu. Tu restes assis près de moi ? Oui, papa. Les chaussettes rouges sont immobiles. Le coussin rayé est encore chaud. La pause a aidé.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1936,7 +1932,6 @@
 papa|La pause a aidé.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,12 +1956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai demandé une pause. J'étais nerveux. Bravo. Tu as fait du bon travail. Le rond jaune de la lampe reste là. L'histoire est finie.</t>
+          <t>J'ai demandé une pause. J'étais nerveux. Bravo. Le rond jaune de la lampe reste là.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai demandé une pause. J'étais nerveux. Bravo. Le rond jaune de la lampe reste là.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2104,12 +2099,9 @@
           <t>enfant-m|J'ai demandé une pause.
 enfant-m|J'étais nerveux.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le rond jaune de la lampe reste là.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le rond jaune de la lampe reste là.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2128,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2173,6 +2165,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>
